--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P23" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI23"/>
+  <dimension ref="A1:BI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46128.65625</v>
+        <v>46128.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46128.66666666666</v>
+        <v>46128.65625</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46128.875</v>
+        <v>46128.66666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -4088,991 +4088,6 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI19" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CS Constantine</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Lokomotiv</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Navbahor</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MB Rouisset</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>El Bayadh</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI23" s="3" t="n">
         <v>46128.875</v>
       </c>
     </row>

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2189,124 +2189,124 @@
         <v>2.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2780,124 +2780,124 @@
         <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.5</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.51</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>3.31</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AW11" t="n">
         <v>1.93</v>
@@ -2682,25 +2682,25 @@
         <v>1.35</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="BA11" t="n">
         <v>2.61</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2180,37 +2180,37 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>3.73</v>
       </c>
       <c r="R9" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
         <v>1.41</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AA9" t="n">
         <v>1.06</v>
@@ -2219,31 +2219,31 @@
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>1.93</v>
@@ -2297,13 +2297,13 @@
         <v>1.21</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BD9" t="n">
         <v>3.68</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="BF9" t="n">
         <v>1.15</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="V12" t="n">
         <v>1.47</v>
@@ -2798,10 +2798,10 @@
         <v>3.16</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.02</v>
@@ -2810,40 +2810,40 @@
         <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AM12" t="n">
         <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -998,64 +998,64 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="S3" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>4.78</v>
+        <v>4.41</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.34</v>
+        <v>3.83</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.89</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG3" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.08</v>
+        <v>5.75</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.07</v>
@@ -1064,10 +1064,10 @@
         <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
         <v>1.65</v>
@@ -1115,16 +1115,16 @@
         <v>1.19</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="BD3" t="n">
         <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2183,61 +2183,61 @@
         <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>4.73</v>
+        <v>4.64</v>
       </c>
       <c r="T9" t="n">
         <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V9" t="n">
         <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.08</v>
@@ -2246,13 +2246,13 @@
         <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,16 +2297,16 @@
         <v>1.21</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BD9" t="n">
         <v>3.68</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1592,22 +1592,22 @@
         <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
         <v>3.02</v>
@@ -1619,7 +1619,7 @@
         <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
         <v>1.09</v>
@@ -1634,34 +1634,34 @@
         <v>3.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
         <v>2.74</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>4.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
         <v>2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
         <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BF6" t="n">
         <v>1.21</v>
@@ -2180,70 +2180,70 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="X9" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>1.97</v>
@@ -2294,16 +2294,16 @@
         <v>1.68</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BF9" t="n">
         <v>1.16</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2577,13 +2577,13 @@
         <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="T11" t="n">
         <v>2.25</v>
@@ -2610,34 +2610,34 @@
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
         <v>2.1</v>
@@ -2646,7 +2646,7 @@
         <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2691,16 +2691,16 @@
         <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,28 +2771,28 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Q12" t="n">
         <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
         <v>3.16</v>
@@ -2807,25 +2807,25 @@
         <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
         <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
         <v>3.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
         <v>8.5</v>
@@ -2837,10 +2837,10 @@
         <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
         <v>1.34</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P17" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -2774,19 +2774,19 @@
         <v>3.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
         <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="V12" t="n">
         <v>1.48</v>
@@ -2813,7 +2813,7 @@
         <v>1.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="AE12" t="n">
         <v>2.25</v>
@@ -2825,7 +2825,7 @@
         <v>3.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
         <v>8.5</v>
@@ -2834,13 +2834,13 @@
         <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
         <v>1.82</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AN12" t="n">
         <v>1.34</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P18" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI18"/>
+  <dimension ref="A1:BI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2186,70 +2186,70 @@
         <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="U9" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD9" t="n">
         <v>3.05</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AK9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL9" t="n">
         <v>1.94</v>
       </c>
-      <c r="AG9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AM9" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AN9" t="n">
         <v>1.22</v>
@@ -2294,19 +2294,19 @@
         <v>1.68</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,16 +2574,16 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
         <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
         <v>2.25</v>
@@ -2607,28 +2607,28 @@
         <v>5.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
         <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2637,7 +2637,7 @@
         <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL11" t="n">
         <v>2.1</v>
@@ -2688,19 +2688,19 @@
         <v>2.61</v>
       </c>
       <c r="BB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,64 +2771,64 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>2.99</v>
       </c>
       <c r="R12" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="X12" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AE12" t="n">
         <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
         <v>3.9</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.02</v>
@@ -2837,10 +2837,10 @@
         <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AN12" t="n">
         <v>1.34</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -3497,597 +3497,6 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Termez Surkhon</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Qizilqum</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AGMK</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Buxoro</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" s="3" t="n">
-        <v>46128.875</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ben Aknoun</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="3" t="n">
         <v>46128.875</v>
       </c>
     </row>

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2180,16 +2180,16 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>4.54</v>
       </c>
       <c r="T9" t="n">
         <v>2.21</v>
@@ -2204,16 +2204,16 @@
         <v>3.02</v>
       </c>
       <c r="X9" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z9" t="n">
         <v>6.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
         <v>1</v>
@@ -2222,22 +2222,22 @@
         <v>1.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AE9" t="n">
         <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
         <v>3.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.07</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
         <v>3.2</v>
@@ -1207,22 +1207,22 @@
         <v>2.63</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="U4" t="n">
-        <v>3.8</v>
+        <v>4.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="X4" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
         <v>6.75</v>
@@ -1234,40 +1234,40 @@
         <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AE4" t="n">
         <v>1.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
         <v>1.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>2.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2180,67 +2180,67 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.8</v>
       </c>
       <c r="S9" t="n">
-        <v>4.54</v>
+        <v>4.66</v>
       </c>
       <c r="T9" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="U9" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="X9" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AH9" t="n">
         <v>1.24</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
         <v>1.8</v>
@@ -2249,7 +2249,7 @@
         <v>1.94</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN9" t="n">
         <v>1.22</v>
@@ -2294,19 +2294,19 @@
         <v>1.68</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6</v>
+        <v>5.23</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>4.78</v>
+        <v>5.43</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="X4" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AH4" t="n">
         <v>1.32</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.05</v>
+        <v>5.45</v>
       </c>
       <c r="AJ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AX4" t="n">
         <v>1.81</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AY4" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.6</v>
+        <v>5.09</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="V5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.3</v>
       </c>
-      <c r="W5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,37 +2180,37 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="Q9" t="n">
         <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S9" t="n">
-        <v>4.66</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
@@ -2219,22 +2219,22 @@
         <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AE9" t="n">
         <v>1.94</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
         <v>3.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI9" t="n">
         <v>6.65</v>
@@ -2243,16 +2243,16 @@
         <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>1.94</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD9" t="n">
         <v>3.36</v>
@@ -2377,52 +2377,52 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AF10" t="n">
         <v>1.38</v>
@@ -2431,79 +2431,79 @@
         <v>4.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,22 +2574,22 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
         <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
         <v>1.34</v>
@@ -2598,55 +2598,55 @@
         <v>3.23</v>
       </c>
       <c r="X11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM11" t="n">
         <v>1.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2661,10 +2661,10 @@
         <v>2.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AU11" t="n">
         <v>3.31</v>
@@ -2673,13 +2673,13 @@
         <v>2.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.78</v>
@@ -2688,19 +2688,19 @@
         <v>2.61</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2774,28 +2774,28 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S12" t="n">
         <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V12" t="n">
         <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="X12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
         <v>1.3</v>
@@ -2810,37 +2810,37 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AD12" t="n">
         <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AF12" t="n">
         <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AN12" t="n">
         <v>1.34</v>
@@ -2849,34 +2849,34 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
         <v>2.15</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -807,73 +807,73 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>4.46</v>
+        <v>3.97</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>5.71</v>
+        <v>5.54</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="X2" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AM2" t="n">
         <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BF2" t="n">
         <v>1.1</v>
@@ -1001,28 +1001,28 @@
         <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R3" t="n">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="S3" t="n">
         <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
         <v>3.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="Y3" t="n">
         <v>1.39</v>
@@ -1034,7 +1034,7 @@
         <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
         <v>1.24</v>
@@ -1043,19 +1043,19 @@
         <v>3.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.07</v>
@@ -1064,52 +1064,52 @@
         <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AR3" t="n">
         <v>1.78</v>
       </c>
       <c r="AS3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV3" t="n">
         <v>2.24</v>
       </c>
-      <c r="AT3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AW3" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.88</v>
+        <v>4.62</v>
       </c>
       <c r="BB3" t="n">
         <v>1.2</v>
@@ -1118,7 +1118,7 @@
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="BE3" t="n">
         <v>1.69</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
         <v>6</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
         <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="X6" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
         <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1864,40 +1864,40 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB7" t="n">
         <v>1.2</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="V8" t="n">
         <v>1.49</v>
@@ -2019,7 +2019,7 @@
         <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC8" t="n">
         <v>1.41</v>
@@ -2028,7 +2028,7 @@
         <v>2.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AF8" t="n">
         <v>1.53</v>
@@ -2040,55 +2040,55 @@
         <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R9" t="n">
         <v>1.85</v>
@@ -2201,7 +2201,7 @@
         <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="X9" t="n">
         <v>2.8</v>
@@ -2210,7 +2210,7 @@
         <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
@@ -2234,13 +2234,13 @@
         <v>3.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI9" t="n">
         <v>6.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
         <v>1.85</v>
@@ -2252,52 +2252,52 @@
         <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="AT9" t="n">
         <v>3.35</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AY9" t="n">
         <v>1.27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="BB9" t="n">
         <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BD9" t="n">
         <v>3.36</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="S10" t="n">
         <v>3.5</v>
@@ -2395,7 +2395,7 @@
         <v>3.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
         <v>2.07</v>
@@ -2410,10 +2410,10 @@
         <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
         <v>1.72</v>
@@ -2425,13 +2425,13 @@
         <v>3.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AG10" t="n">
         <v>4.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" t="n">
         <v>12.5</v>
@@ -2443,7 +2443,7 @@
         <v>2.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AM10" t="n">
         <v>1.35</v>
@@ -2461,10 +2461,10 @@
         <v>2.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.78</v>
+        <v>3.73</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.46</v>
@@ -2491,13 +2491,13 @@
         <v>2.56</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="BE10" t="n">
         <v>1.28</v>
@@ -2574,22 +2574,22 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="V11" t="n">
         <v>1.34</v>
@@ -2607,100 +2607,100 @@
         <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
         <v>1.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AH11" t="n">
         <v>1.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL11" t="n">
         <v>2.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R12" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
         <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="V12" t="n">
         <v>1.42</v>
@@ -2798,7 +2798,7 @@
         <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
         <v>8.199999999999999</v>
@@ -2810,13 +2810,13 @@
         <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD12" t="n">
         <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AF12" t="n">
         <v>1.62</v>
@@ -2825,22 +2825,22 @@
         <v>4.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL12" t="n">
         <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN12" t="n">
         <v>1.34</v>
@@ -2849,19 +2849,19 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.51</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AS12" t="n">
         <v>2.38</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AU12" t="n">
         <v>3.26</v>
@@ -2876,7 +2876,7 @@
         <v>1.49</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AZ12" t="n">
         <v>2.15</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.13</v>
+        <v>3.85</v>
       </c>
       <c r="R3" t="n">
-        <v>4.15</v>
+        <v>5.23</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC3" t="n">
         <v>1.97</v>
       </c>
-      <c r="U3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2</v>
-      </c>
       <c r="BD3" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.85</v>
       </c>
-      <c r="R4" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5.43</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="BC4" t="n">
         <v>2</v>
       </c>
-      <c r="AG4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="BD4" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.69</v>
       </c>
-      <c r="AS4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,112 +1392,112 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
         <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="T6" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI6" t="n">
         <v>6</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
         <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,112 +1392,112 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
         <v>6</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
         <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>4.02</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
         <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AM6" t="n">
         <v>1.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="X7" t="n">
         <v>2.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
         <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AN7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC7" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1001,10 +1001,10 @@
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R3" t="n">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
         <v>2.16</v>
@@ -1025,7 +1025,7 @@
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z3" t="n">
         <v>6</v>
@@ -1037,19 +1037,19 @@
         <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
         <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
         <v>1.32</v>
@@ -1064,7 +1064,7 @@
         <v>1.77</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AM3" t="n">
         <v>1.19</v>
@@ -1076,40 +1076,40 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX3" t="n">
         <v>1.69</v>
       </c>
-      <c r="AS3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AY3" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.09</v>
+        <v>4.53</v>
       </c>
       <c r="BB3" t="n">
         <v>1.16</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,112 +1392,112 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="X5" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
         <v>1.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,112 +1786,112 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="U7" t="n">
-        <v>3.96</v>
+        <v>3.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="X7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AL7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW7" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AX7" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="R2" t="n">
-        <v>3.97</v>
+        <v>4.07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>5.54</v>
+        <v>4.25</v>
       </c>
       <c r="V2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.5</v>
       </c>
-      <c r="W2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG2" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AM2" t="n">
         <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>5.43</v>
+        <v>3.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.45</v>
+        <v>6.35</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
         <v>1.95</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.06</v>
+        <v>2.59</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.82</v>
+        <v>2.96</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.64</v>
+        <v>2.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.53</v>
+        <v>4.63</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1.97</v>
       </c>
-      <c r="U4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
       <c r="BD4" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.98</v>
+        <v>2.39</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>3.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>3.96</v>
+        <v>2.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
         <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI5" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW6" t="n">
         <v>2.05</v>
       </c>
-      <c r="AG6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AX6" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1789,110 +1789,110 @@
         <v>2.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>2.97</v>
+        <v>2.41</v>
       </c>
       <c r="X7" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.45</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AN7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
         <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AM8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.33</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AR8" t="n">
         <v>2.82</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BF8" t="n">
         <v>1.1</v>
@@ -2180,37 +2180,37 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="S9" t="n">
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>2.73</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
@@ -2222,88 +2222,88 @@
         <v>1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AM9" t="n">
         <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BB9" t="n">
         <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BD9" t="n">
         <v>3.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF9" t="n">
         <v>1.12</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="S10" t="n">
         <v>3.5</v>
@@ -2392,7 +2392,7 @@
         <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="V10" t="n">
         <v>1.67</v>
@@ -2407,28 +2407,28 @@
         <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
         <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
         <v>2.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AH10" t="n">
         <v>1.04</v>
@@ -2461,10 +2461,10 @@
         <v>2.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.73</v>
+        <v>2.78</v>
       </c>
       <c r="AS10" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="AT10" t="n">
         <v>6.46</v>
@@ -2473,13 +2473,13 @@
         <v>2.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AW10" t="n">
         <v>1.34</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AY10" t="n">
         <v>1.03</v>
@@ -2494,7 +2494,7 @@
         <v>1.43</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="BD10" t="n">
         <v>2.53</v>
@@ -2771,37 +2771,37 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U12" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AA12" t="n">
         <v>1.02</v>
@@ -2816,7 +2816,7 @@
         <v>2.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AF12" t="n">
         <v>1.62</v>
@@ -2840,7 +2840,7 @@
         <v>1.85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AN12" t="n">
         <v>1.34</v>
@@ -2852,28 +2852,28 @@
         <v>1.26</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AY12" t="n">
         <v>1.36</v>
@@ -2888,13 +2888,13 @@
         <v>1.28</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="BD12" t="n">
         <v>3.25</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BF12" t="n">
         <v>1.09</v>

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="R5" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="S5" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.92</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.61</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.03</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AQ5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="S6" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN6" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z6" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1789,109 +1789,109 @@
         <v>2.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>2.41</v>
+        <v>2.97</v>
       </c>
       <c r="X7" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1.66</v>
       </c>
-      <c r="AG7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AY7" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="X6" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="V7" t="n">
         <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN7" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z7" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -1166,51 +1166,51 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>5.43</v>
+        <v>5.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1219,13 +1219,13 @@
         <v>2.91</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA4" t="n">
         <v>1.05</v>
@@ -1237,91 +1237,91 @@
         <v>1.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
         <v>3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
         <v>1.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1395,109 +1395,109 @@
         <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="U5" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>2.41</v>
+        <v>2.97</v>
       </c>
       <c r="X5" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX5" t="n">
         <v>1.66</v>
       </c>
-      <c r="AG5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AY5" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.45</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF6" t="n">
         <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" t="n">
         <v>5.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.7</v>
+        <v>3.17</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="X7" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC7" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -787,90 +787,90 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>4.07</v>
+        <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>4.25</v>
+        <v>4.83</v>
       </c>
       <c r="V2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AC2" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AN2" t="n">
         <v>1.74</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -987,144 +987,144 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.73</v>
+        <v>2.98</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.35</v>
+        <v>7.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="BE3" t="n">
         <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1378,127 +1378,127 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL5" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AM5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1572,135 +1572,135 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
         <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.7</v>
+        <v>6.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
         <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>1.22</v>
@@ -1709,13 +1709,13 @@
         <v>1.95</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,171 +1748,171 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="S7" t="n">
         <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6</v>
+        <v>3.02</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU7" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK7" t="n">
+      <c r="AV7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,70 +1983,70 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="R8" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
         <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL8" t="n">
         <v>1.73</v>
@@ -2055,7 +2055,7 @@
         <v>1.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AR8" t="n">
         <v>2.82</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
         <v>1.1</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG9" t="n">
         <v>4.2</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AH9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM9" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z9" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AN9" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.22</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>1.74</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AS9" t="n">
         <v>2.94</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="AU9" t="n">
         <v>2.63</v>
@@ -2282,31 +2282,31 @@
         <v>1.59</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AY9" t="n">
         <v>1.14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.87</v>
+        <v>3.21</v>
       </c>
       <c r="S10" t="n">
         <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>4.14</v>
+        <v>3.85</v>
       </c>
       <c r="V10" t="n">
         <v>1.67</v>
@@ -2401,13 +2401,13 @@
         <v>2.07</v>
       </c>
       <c r="X10" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
         <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.01</v>
@@ -2416,25 +2416,25 @@
         <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.02</v>
@@ -2446,10 +2446,10 @@
         <v>1.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>2.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AS10" t="n">
         <v>4.12</v>
@@ -2470,10 +2470,10 @@
         <v>6.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AW10" t="n">
         <v>1.34</v>
@@ -2491,19 +2491,19 @@
         <v>2.56</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2774,109 +2774,109 @@
         <v>2.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="S12" t="n">
-        <v>3.93</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="X12" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
         <v>1.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.42</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AT12" t="n">
         <v>2.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AV12" t="n">
         <v>2.58</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AZ12" t="n">
         <v>2.15</v>
@@ -2885,19 +2885,19 @@
         <v>1.81</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,171 +960,171 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
+        <v>9</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+      <c r="AH3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AM3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,171 +1157,171 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="AE4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="AF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV4" t="n">
         <v>2.15</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AW4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC4" t="n">
         <v>2.25</v>
       </c>
-      <c r="U4" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BD4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.57</v>
       </c>
-      <c r="AY4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1541,32 +1541,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1589,118 +1589,118 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
         <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
         <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1.89</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>1.22</v>
@@ -1709,13 +1709,13 @@
         <v>1.95</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,32 +1738,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1772,13 +1772,13 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1786,118 +1786,118 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="R7" t="n">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
         <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="X7" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.7</v>
+        <v>6.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
         <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>1.22</v>
@@ -1906,13 +1906,13 @@
         <v>1.95</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1972,14 +1972,14 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2169,14 +2169,14 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2360,20 +2360,20 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2545,66 +2545,66 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA11" t="n">
         <v>1.12</v>
@@ -2613,94 +2613,94 @@
         <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="n">
         <v>1.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM11" t="n">
         <v>1.16</v>
       </c>
-      <c r="AK11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
         <v>2.2</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1.19</v>
       </c>
-      <c r="AN11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="AV11" t="n">
         <v>2.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.56</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-04-16.xlsx
+++ b/jogos_2026-04-16.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,171 +960,171 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="AE3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="AF3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV3" t="n">
         <v>2.15</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AW3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.25</v>
       </c>
-      <c r="U3" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX3" t="n">
+      <c r="BD3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.57</v>
       </c>
-      <c r="AY3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,171 +1157,171 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="AH4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AM4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -2760,14 +2760,14 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
